--- a/healthcare_surveys/041_patient_safety_assessment_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/041_patient_safety_assessment_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form</t>
+          <t>patient_safety_risks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form</t>
+          <t>What are the perceived safety risks to the patient?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_1</t>
+          <t>patient_safety_suggestions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>patient_safety</t>
+          <t>How would you suggest patient safety protocols?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_2</t>
+          <t>patient_safety_response</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>safety_risks</t>
+          <t>How safe do you feel when receiving care from our healthcare team?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_3</t>
+          <t>patient_safety_team_interactions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>safety_risks_1</t>
+          <t>How safe do you feel when interacting with our healthcare team?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_4</t>
+          <t>safety_incidents</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>patient_safety_risk_4</t>
+          <t>Have you experienced any safety incidents or near misses?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_5</t>
+          <t>patient_safety_training</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>safety_risks_5</t>
+          <t>Do you feel we provide adequate training on patient safety?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_6</t>
+          <t>safety_issues</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>patient_safety_suggest</t>
+          <t>Have you noticed any safety-related issues or concerns?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_7</t>
+          <t>patient_safety_perception</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>patient_safety_protocol</t>
+          <t>What is your overall perception of patient safety in our healthcare setting?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_8</t>
+          <t>patient_safety_suggestions_improve</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>safety_risks_8</t>
+          <t>What is your experience with reporting safety incidents in our healthcare setting?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_9</t>
+          <t>patient_safety_protocol_implement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>patient_safety_protocol_1</t>
+          <t>What safety protocols do you suggest we implement to prevent future incidents?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_10</t>
+          <t>patient_safety_response_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>safety_risks_10</t>
+          <t>Patient Safety Response Time</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_11</t>
+          <t>patient_safety_suggestions_improvement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>patient_safety_survey_response</t>
+          <t>Do you have any safety-related suggestions for improvement?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_12</t>
+          <t>patient_safety_reporting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>safety_risks_11</t>
+          <t>Patient Safety Reporting</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_13</t>
+          <t>patient_safety_response_protocol</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>patient_safety_protocol_2</t>
+          <t>How do you feel about our response to patient safety concerns?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_14</t>
+          <t>patient_safety_suggestions_improve_incident</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>safety_risks_12</t>
+          <t>What safety-related incidents have you noticed?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_15</t>
+          <t>patient_safety_suggestions_improvement_incident</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>patient_safety_protocol_3</t>
+          <t>Patient Safety Suggestions Improvement Incident</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_16</t>
+          <t>patient_safety_response_time_protocol</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>safety_risks_13</t>
+          <t>Patient Safety Response Time Protocol</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,522 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_17</t>
+          <t>patient_safety_response_concerns</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>patient_safety_protocol_4</t>
+          <t>What is your feedback on our response to patient safety concerns?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>patient_safety_response</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>safety_risks_14</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_5</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>safety_risks_15</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_6</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>safety_risks_16</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_24</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_25</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_3</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_26</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_4</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_27</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_5</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_28</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_6</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_29</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_7</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_30</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_8</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_31</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_9</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_32</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_10</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_33</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_11</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_34</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_12</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_35</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_13</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_36</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_14</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_37</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_15</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_38</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>patient_safety_protocol_16</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1443,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1471,204 +965,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_2_choices</t>
+          <t>patient_safety_team_interactions_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_2_choices</t>
+          <t>patient_safety_team_interactions_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_2_choices</t>
+          <t>patient_safety_team_interactions_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_3_choices</t>
+          <t>patient_safety_training_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_3_choices</t>
+          <t>patient_safety_training_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_3_choices</t>
+          <t>patient_safety_training_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_9_choices</t>
+          <t>patient_safety_response_protocol_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_9_choices</t>
+          <t>patient_safety_response_protocol_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>mostly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Mostly</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_9_choices</t>
+          <t>patient_safety_response_protocol_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_20_choices</t>
+          <t>patient_safety_response_protocol_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>patient_safety_survey_form_20_choices</t>
+          <t>patient_safety_response_protocol_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>patient_safety_survey_form_20_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
